--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486944_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486944_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1501</v>
+        <v>7.2367</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1263</v>
+        <v>5.6576</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0238</v>
+        <v>1.5792</v>
       </c>
       <c r="G2" t="n">
         <v>0.4706</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5706</v>
+        <v>1.6573</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1698</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4008</v>
+        <v>0.9562</v>
       </c>
       <c r="V2" t="n">
         <v>3.0554</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.071</v>
+        <v>4.1577</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3746</v>
+        <v>3.936</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6963</v>
+        <v>0.2217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0048</v>
+        <v>3.2172</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5019</v>
+        <v>3.854</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.497</v>
+        <v>-0.6368</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9561</v>
+        <v>4.4901</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9695</v>
+        <v>3.9905</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0134</v>
+        <v>0.4997</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9512</v>
+        <v>-1.2729</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4676</v>
+        <v>-0.1365</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4836</v>
+        <v>-1.1365</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2855</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1626</v>
+        <v>0.5298</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4987</v>
+        <v>0.2324</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6639</v>
+        <v>0.2974</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1184</v>
+        <v>2.2828</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0449</v>
+        <v>-0.206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0735</v>
+        <v>2.4888</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2172</v>
+        <v>0.0048</v>
       </c>
       <c r="H4" t="n">
-        <v>3.854</v>
+        <v>1.5019</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6368</v>
+        <v>-1.497</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4901</v>
+        <v>1.9561</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9905</v>
+        <v>1.9695</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4997</v>
+        <v>-0.0134</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2729</v>
+        <v>-1.9512</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1365</v>
+        <v>-0.4676</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1365</v>
+        <v>-1.4836</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>3.2855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5095</v>
+        <v>1.3745</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6587</v>
+        <v>0.918</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1492</v>
+        <v>0.4564</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7398</v>
+        <v>1.0033</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1839</v>
+        <v>0.0796</v>
       </c>
       <c r="F5" t="n">
         <v>0.9237</v>
@@ -844,10 +844,10 @@
         <v>3.4908</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1395</v>
+        <v>0.403</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2749</v>
+        <v>0.5384</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1354</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3778</v>
+        <v>-0.3947</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0035</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3813</v>
+        <v>-0.3947</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6462</v>
+        <v>-0.3947</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0702</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.576</v>
+        <v>-0.3947</v>
       </c>
       <c r="J6" t="n">
-        <v>0.787</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5153</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3024</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4332</v>
+        <v>-0.3947</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.8783</v>
+        <v>-0.3947</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1801</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3947</v>
+        <v>-0.6208</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.6122</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3947</v>
+        <v>-2.2331</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3947</v>
+        <v>-2.6462</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.0702</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3947</v>
+        <v>-1.576</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.787</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.5153</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.3024</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3947</v>
+        <v>-3.4332</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3947</v>
+        <v>-2.8783</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.3128</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3447</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.0319</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3423</v>
+        <v>-0.9735</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1183</v>
+        <v>-0.8088</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2239</v>
+        <v>-0.1646</v>
       </c>
       <c r="G8" t="n">
         <v>-4.4818</v>
@@ -1078,13 +1078,13 @@
         <v>3.9015</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2157</v>
+        <v>0.1531</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1198</v>
+        <v>0.1897</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0959</v>
+        <v>-0.0366</v>
       </c>
       <c r="V8" t="n">
         <v>0.4805</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6888</v>
+        <v>-1.1051</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7259</v>
+        <v>0.4131</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9628</v>
+        <v>-1.5182</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2629</v>
@@ -1156,13 +1156,13 @@
         <v>3.9015</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7997</v>
+        <v>-0.216</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2516</v>
+        <v>-0.1125</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5481</v>
+        <v>-0.1035</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5277</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5752</v>
+        <v>-4.2391</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8818</v>
+        <v>-4.3975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3065</v>
+        <v>0.1583</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5664</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8116</v>
+        <v>-0.4755</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.527</v>
+        <v>-0.0427</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2846</v>
+        <v>-0.4328</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3491</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.700500000000001</v>
+        <v>7.347300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6394</v>
+        <v>6.2862</v>
       </c>
       <c r="F11" t="n">
-        <v>1.061100000000001</v>
+        <v>1.0611</v>
       </c>
       <c r="G11" t="n">
         <v>-9.210899999999999</v>
@@ -1312,10 +1312,10 @@
         <v>21.561</v>
       </c>
       <c r="S11" t="n">
-        <v>2.0921</v>
+        <v>3.739</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1223</v>
+        <v>2.7691</v>
       </c>
       <c r="U11" t="n">
         <v>0.9698</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.168</v>
+        <v>11.4975</v>
       </c>
       <c r="E12" t="n">
-        <v>11.3041</v>
+        <v>11.7225</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1361</v>
+        <v>-0.225</v>
       </c>
       <c r="G12" t="n">
         <v>11.548</v>
@@ -1390,13 +1390,13 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0166</v>
+        <v>0.3129</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0504</v>
+        <v>0.368</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0338</v>
+        <v>-0.0551</v>
       </c>
       <c r="V12" t="n">
         <v>0.4579</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1952</v>
+        <v>1.4341</v>
       </c>
       <c r="E13" t="n">
-        <v>2.186</v>
+        <v>2.3952</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9908</v>
+        <v>-0.9611</v>
       </c>
       <c r="G13" t="n">
         <v>2.8751</v>
@@ -1468,13 +1468,13 @@
         <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5648</v>
+        <v>-1.326</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.6975</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6581</v>
+        <v>-0.6284</v>
       </c>
       <c r="V13" t="n">
         <v>1.5277</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1326</v>
+        <v>0.5799</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3916</v>
+        <v>-0.2882</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5242</v>
+        <v>0.8681</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3897</v>
+        <v>0.8454</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0678</v>
+        <v>-0.2045</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4575</v>
+        <v>1.0499</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2986</v>
+        <v>1.4631</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0618</v>
+        <v>0.0423</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2368</v>
+        <v>1.4208</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6883</v>
+        <v>-0.6177</v>
       </c>
       <c r="N14" t="n">
-        <v>0.006</v>
+        <v>-0.2468</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6943</v>
+        <v>-0.3709</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2902</v>
+        <v>0.5908</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6856</v>
+        <v>0.3021</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6046</v>
+        <v>0.2887</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2402</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4021</v>
+        <v>0.2085</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2882</v>
+        <v>-1.0192</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6903</v>
+        <v>1.2278</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8454</v>
+        <v>-0.3897</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2045</v>
+        <v>0.0678</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0499</v>
+        <v>-0.4575</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4631</v>
+        <v>0.2986</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0423</v>
+        <v>0.0618</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4208</v>
+        <v>0.2368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6177</v>
+        <v>-0.6883</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2468</v>
+        <v>0.006</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3709</v>
+        <v>-0.6943</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>0.413</v>
+        <v>0.3662</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3021</v>
+        <v>0.0579</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1108</v>
+        <v>0.3082</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0956</v>
+        <v>-0.4118</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3578</v>
+        <v>0.9394</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2622</v>
+        <v>-1.3512</v>
       </c>
       <c r="G16" t="n">
         <v>0.5121</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3514</v>
+        <v>-0.1559</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1045</v>
+        <v>-0.3139</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2469</v>
+        <v>0.158</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0529</v>
+        <v>-0.6815</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1929</v>
+        <v>0.2975</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2458</v>
+        <v>-0.979</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2567</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5622</v>
+        <v>-0.1908</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2517</v>
+        <v>0.3563</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8139</v>
+        <v>-0.5471</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8768</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3533</v>
+        <v>-2.2713</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5684</v>
+        <v>-2.9962</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2151</v>
+        <v>0.7249</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6298</v>
+        <v>-0.5526</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0379</v>
+        <v>-2.381</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4081</v>
+        <v>1.8285</v>
       </c>
       <c r="J18" t="n">
-        <v>1.158</v>
+        <v>0.3204</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8687</v>
+        <v>-1.9947</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7108</v>
+        <v>2.3151</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5281</v>
+        <v>-0.8729</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8308</v>
+        <v>-0.3863</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3027</v>
+        <v>-0.4866</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.6962</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.3122</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4657</v>
+        <v>-0.3429</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5928</v>
+        <v>-0.4767</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1272</v>
+        <v>0.1338</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5258</v>
+        <v>-2.308</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.31</v>
+        <v>-2.4638</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7842</v>
+        <v>0.1558</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5526</v>
+        <v>0.6298</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.381</v>
+        <v>1.0379</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8285</v>
+        <v>-0.4081</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3204</v>
+        <v>1.158</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9947</v>
+        <v>1.8687</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3151</v>
+        <v>-0.7108</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8729</v>
+        <v>-0.5281</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3863</v>
+        <v>-0.8308</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4866</v>
+        <v>0.3027</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0267</v>
+        <v>-3.6962</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-4.3122</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5974</v>
+        <v>-0.4203</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7905</v>
+        <v>-0.4882</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1931</v>
+        <v>0.0679</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0976</v>
+        <v>-4.0087</v>
       </c>
       <c r="E20" t="n">
         <v>-3.3778</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7198</v>
+        <v>-0.6309</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1546</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6226</v>
+        <v>-0.5337</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3294</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2933</v>
+        <v>-0.2043</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5278</v>
+        <v>-4.1564</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4809</v>
+        <v>-3.3763</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0469</v>
+        <v>-0.7801</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4189</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5545</v>
+        <v>-0.1831</v>
       </c>
       <c r="T21" t="n">
-        <v>0.12</v>
+        <v>0.2246</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6744</v>
+        <v>-0.4076</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9384</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1366</v>
+        <v>-5.583</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.685</v>
+        <v>-2.8942</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4516</v>
+        <v>-2.6888</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4272</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2371</v>
+        <v>-0.2092</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2362</v>
+        <v>0.027</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0009</v>
+        <v>-0.2362</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3573</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.700499999999999</v>
+        <v>-5.7007</v>
       </c>
       <c r="E23" t="n">
         <v>-1.061100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6394</v>
+        <v>-4.6395</v>
       </c>
       <c r="G23" t="n">
         <v>9.210699999999999</v>
@@ -2248,13 +2248,13 @@
         <v>13.3472</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0921</v>
+        <v>-2.092</v>
       </c>
       <c r="T23" t="n">
         <v>-0.9698</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1224</v>
+        <v>-1.1221</v>
       </c>
       <c r="V23" t="n">
         <v>-4.605700000000001</v>
